--- a/Result/profitability/3588.xlsx
+++ b/Result/profitability/3588.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32125</v>
+        <v>0.30125</v>
       </c>
       <c r="N2" t="n">
-        <v>35.56875</v>
+        <v>35.40625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0.46</v>
+        <v>0.5149999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>35.95625</v>
+        <v>35.7575</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.67375</v>
+        <v>0.7174999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>36.17125</v>
+        <v>36.25</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7325</v>
+        <v>0.8062499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>36.6975</v>
+        <v>36.555</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8025</v>
+        <v>0.87</v>
       </c>
       <c r="N6" t="n">
-        <v>37.17</v>
+        <v>37.96</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9837499999999999</v>
+        <v>1.045</v>
       </c>
       <c r="N7" t="n">
-        <v>38.47875</v>
+        <v>39.10375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>1.23625</v>
+        <v>1.2675</v>
       </c>
       <c r="N8" t="n">
-        <v>39.59875</v>
+        <v>39.97625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>434</v>
+      </c>
+      <c r="D75" t="n">
+        <v>275</v>
+      </c>
+      <c r="E75" t="n">
+        <v>159</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.2625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.020000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08985421005653094</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>19.66666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.140000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03018268467037333</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
